--- a/qa/manual/test-cases/Database/Database_testCase.xlsx
+++ b/qa/manual/test-cases/Database/Database_testCase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\freeSpace-main\qa\manual\test-cases\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7150EC-F03A-4115-8F46-CBDA5B1BD1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8316D57D-0740-4956-BD50-EC63B0FCACD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'DB Device Identities'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DB Map Notes'!$A$1:$I$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DB Postcards'!$A$1:$I$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DB Posts'!$A$1:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DB Posts'!$A$1:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DB Reported Posts'!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'DB Settings'!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Test Data'!$A$1:$E$26</definedName>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="347">
   <si>
     <t>TC ID</t>
   </si>
@@ -81,111 +81,6 @@
   </si>
   <si>
     <t>Test Data</t>
-  </si>
-  <si>
-    <t>TC_DBI_01</t>
-  </si>
-  <si>
-    <t>Verify posting with a new name locks the identity in the database</t>
-  </si>
-  <si>
-    <t>1. VentSpace app is running at http://localhost:5173.
-2. Supabase Dashboard (SQL Editor or Table Editor) is open.
-3. The device has no locked name yet.</t>
-  </si>
-  <si>
-    <t>1. Create a post with the name DBIdentityTester.
-2. Run the SQL query.</t>
-  </si>
-  <si>
-    <t>SELECT * FROM device_identities WHERE username = 'DBIdentityTester';</t>
-  </si>
-  <si>
-    <t>One row exists with the device's uuid and the username DBIdentityTester.</t>
-  </si>
-  <si>
-    <t>TD_DB_22</t>
-  </si>
-  <si>
-    <t>TC_DBI_02</t>
-  </si>
-  <si>
-    <t>Verify the locked name is reused for the next post (single row)</t>
-  </si>
-  <si>
-    <t>1. The identity row exists (TC_DBI_01).</t>
-  </si>
-  <si>
-    <t>1. Create a second post from the same device.
-2. Run the SQL query.</t>
-  </si>
-  <si>
-    <t>SELECT COUNT(*) FROM device_identities WHERE device_id = '&lt;TEST_DEVICE_ID&gt;';</t>
-  </si>
-  <si>
-    <t>The count returns 1 — the same row is reused, no duplicate created.</t>
-  </si>
-  <si>
-    <t>TC_DBI_03</t>
-  </si>
-  <si>
-    <t>Verify an admin name-unlock deletes the identity row</t>
-  </si>
-  <si>
-    <t>1. The identity row exists.
-2. Admin can log in.</t>
-  </si>
-  <si>
-    <t>1. In /admin, run Reset All Hours (or RESET user).
-2. Run the SQL query.</t>
-  </si>
-  <si>
-    <t>SELECT COUNT(*) FROM device_identities WHERE username = 'DBIdentityTester';</t>
-  </si>
-  <si>
-    <t>The count returns 0 — the lock was cleared and the device can pick a new name.</t>
-  </si>
-  <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>Total TC</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Progress</t>
-  </si>
-  <si>
-    <t>DB Posts</t>
-  </si>
-  <si>
-    <t>DB Comments</t>
-  </si>
-  <si>
-    <t>DB Reported Posts</t>
-  </si>
-  <si>
-    <t>DB Map Notes</t>
-  </si>
-  <si>
-    <t>DB Postcards</t>
-  </si>
-  <si>
-    <t>DB Bug Reports</t>
-  </si>
-  <si>
-    <t>DB Device Identities</t>
-  </si>
-  <si>
-    <t>DB Settings</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
   </si>
   <si>
     <t>TC_DBP_01</t>
@@ -213,6 +108,12 @@
     <t>The query returns exactly one row with username = DBTester, mood = Happy, is_deleted = false, likes = 0.</t>
   </si>
   <si>
+    <t xml:space="preserve">	As expected.</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>TD_DB_01, TD_DB_02, TD_DB_03</t>
   </si>
   <si>
@@ -249,6 +150,12 @@
 3. Run the SQL query.</t>
   </si>
   <si>
+    <t>SELECT reactions FROM posts WHERE text = 'My first DB test post';</t>
+  </si>
+  <si>
+    <t>The reactions column returns the count increased by one, matching the number shown in the UI.</t>
+  </si>
+  <si>
     <t>TD_DB_01</t>
   </si>
   <si>
@@ -263,9 +170,6 @@
 3. Run the SQL query.</t>
   </si>
   <si>
-    <t>SELECT reactions FROM posts WHERE text = 'My first DB test post';</t>
-  </si>
-  <si>
     <t>The reactions jsonb contains the heart emoji key with count 1.</t>
   </si>
   <si>
@@ -294,23 +198,43 @@
     <t>TC_DBP_06</t>
   </si>
   <si>
-    <t>Verify deleting a post cascades to its comments in the database</t>
-  </si>
-  <si>
-    <t>1. A test post exists with at least one comment (see DB Comments tab).</t>
-  </si>
-  <si>
-    <t>1. In the admin panel, hard-delete the test post (or delete via SQL).
+    <t>Verify app delete soft-deletes the post and keeps its comments in the database</t>
+  </si>
+  <si>
+    <t>1. VentSpace app is running at http://localhost:5173.
+2. Supabase Dashboard (SQL Editor or Table Editor) is open.
+3. A test post with at least one comment exists.</t>
+  </si>
+  <si>
+    <t>1. In the feed, click Delete on the test post and confirm.
+2. Run the post-row query.
+3. Run the comment-count query.</t>
+  </si>
+  <si>
+    <t>SELECT id, is_deleted FROM posts WHERE text = 'My first DB test post';
+SELECT COUNT(*) FROM comments WHERE post_id = &lt;TEST_POST_ID&gt;;</t>
+  </si>
+  <si>
+    <t>The post row still exists with is_deleted = true, and the comment count returns 0 — the delete also removed its comments and its report-queue entry.</t>
+  </si>
+  <si>
+    <t>TC_DBP_07</t>
+  </si>
+  <si>
+    <t>Verify hard-deleting a post cascades to its comments in the database</t>
+  </si>
+  <si>
+    <t>1. In Supabase SQL Editor, run: DELETE FROM posts WHERE id = &lt;TEST_POST_ID&gt;;
 2. Run the SQL query.</t>
   </si>
   <si>
     <t>SELECT COUNT(*) FROM comments WHERE post_id = &lt;TEST_POST_ID&gt;;</t>
   </si>
   <si>
-    <t>The count returns 0 — comments were removed automatically via cascade.</t>
-  </si>
-  <si>
-    <t>TC_DBP_07</t>
+    <t>The count returns 0 — the comments were removed automatically via cascade.</t>
+  </si>
+  <si>
+    <t>TC_DBP_08</t>
   </si>
   <si>
     <t>Verify the posts rate limit is enforced per device in the database</t>
@@ -333,7 +257,7 @@
     <t>TD_DB_05</t>
   </si>
   <si>
-    <t>TC_DBP_08</t>
+    <t>TC_DBP_09</t>
   </si>
   <si>
     <t>Verify a blacklisted word in a post is rejected and not saved</t>
@@ -356,6 +280,72 @@
     <t>TD_DB_06</t>
   </si>
   <si>
+    <t>TC_DBP_10</t>
+  </si>
+  <si>
+    <t>Verify deleting a reported post also clears its report-queue entry</t>
+  </si>
+  <si>
+    <t>1. VentSpace app is running at http://localhost:5173.
+2. Supabase Dashboard (SQL Editor or Table Editor) is open.
+3. A test post is reported (flagged via the app).</t>
+  </si>
+  <si>
+    <t>1. In the feed, click Delete on the reported test post and confirm.
+2. Run the SQL query.</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM reported_posts WHERE post_id = &lt;TEST_POST_ID&gt;;</t>
+  </si>
+  <si>
+    <t>The count returns 0 — the delete removed the report entry along with the post's comments.</t>
+  </si>
+  <si>
+    <t>TD_DB_10</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Total TC</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Progress</t>
+  </si>
+  <si>
+    <t>DB Posts</t>
+  </si>
+  <si>
+    <t>DB Comments</t>
+  </si>
+  <si>
+    <t>DB Reported Posts</t>
+  </si>
+  <si>
+    <t>DB Map Notes</t>
+  </si>
+  <si>
+    <t>DB Postcards</t>
+  </si>
+  <si>
+    <t>DB Bug Reports</t>
+  </si>
+  <si>
+    <t>DB Device Identities</t>
+  </si>
+  <si>
+    <t>DB Settings</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
     <t>TC_DBPCM_01</t>
   </si>
   <si>
@@ -481,9 +471,6 @@
     <t>One row exists with the correct post_id and a created_at timestamp.</t>
   </si>
   <si>
-    <t>TD_DB_10</t>
-  </si>
-  <si>
     <t>TC_DBR_02</t>
   </si>
   <si>
@@ -510,9 +497,6 @@
   <si>
     <t>1. In the app, un-report the same post.
 2. Run the SQL query.</t>
-  </si>
-  <si>
-    <t>SELECT COUNT(*) FROM reported_posts WHERE post_id = &lt;TEST_POST_ID&gt;;</t>
   </si>
   <si>
     <t>The count returns 0 — the report row was deleted.</t>
@@ -819,6 +803,69 @@
     <t>SELECT COUNT(*) FROM bug_reports WHERE text = 'DB bug report test';</t>
   </si>
   <si>
+    <t>TC_DBI_01</t>
+  </si>
+  <si>
+    <t>Verify posting with a new name locks the identity in the database</t>
+  </si>
+  <si>
+    <t>1. VentSpace app is running at http://localhost:5173.
+2. Supabase Dashboard (SQL Editor or Table Editor) is open.
+3. The device has no locked name yet.</t>
+  </si>
+  <si>
+    <t>1. Create a post with the name DBIdentityTester.
+2. Run the SQL query.</t>
+  </si>
+  <si>
+    <t>SELECT * FROM device_identities WHERE username = 'DBIdentityTester';</t>
+  </si>
+  <si>
+    <t>One row exists with the device's uuid and the username DBIdentityTester.</t>
+  </si>
+  <si>
+    <t>TD_DB_22</t>
+  </si>
+  <si>
+    <t>TC_DBI_02</t>
+  </si>
+  <si>
+    <t>Verify the locked name is reused for the next post (single row)</t>
+  </si>
+  <si>
+    <t>1. The identity row exists (TC_DBI_01).</t>
+  </si>
+  <si>
+    <t>1. Create a second post from the same device.
+2. Run the SQL query.</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM device_identities WHERE device_id = '&lt;TEST_DEVICE_ID&gt;';</t>
+  </si>
+  <si>
+    <t>The count returns 1 — the same row is reused, no duplicate created.</t>
+  </si>
+  <si>
+    <t>TC_DBI_03</t>
+  </si>
+  <si>
+    <t>Verify an admin name-unlock deletes the identity row</t>
+  </si>
+  <si>
+    <t>1. The identity row exists.
+2. Admin can log in.</t>
+  </si>
+  <si>
+    <t>1. In /admin, run Reset All Hours (or RESET user).
+2. Run the SQL query.</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM device_identities WHERE username = 'DBIdentityTester';</t>
+  </si>
+  <si>
+    <t>The count returns 0 — the lock was cleared and the device can pick a new name.</t>
+  </si>
+  <si>
     <t>TC_DBS_01</t>
   </si>
   <si>
@@ -918,7 +965,7 @@
     <t>Valid</t>
   </si>
   <si>
-    <t>TC_DBP_01, TC_DBP_02, TC_DBP_03, TC_DBP_04, TC_DBP_05</t>
+    <t>TC_DBP_01, TC_DBP_02, TC_DBP_05, TC_DBP_06, TC_DBP_07</t>
   </si>
   <si>
     <t>TD_DB_02</t>
@@ -963,7 +1010,7 @@
     <t>testban</t>
   </si>
   <si>
-    <t>TC_DBP_08, TC_DBS_02</t>
+    <t>TC_DBP_09, TC_DBS_02</t>
   </si>
   <si>
     <t>Comment Text</t>
@@ -993,7 +1040,7 @@
     <t>The TC_DBP_01 test post flagged</t>
   </si>
   <si>
-    <t>TC_DBR_01, TC_DBR_02, TC_DBR_03, TC_DBR_04</t>
+    <t>TC_DBR_01, TC_DBR_02, TC_DBR_03, TC_DBR_04, TC_DBP_10</t>
   </si>
   <si>
     <t>TD_DB_11</t>
@@ -1122,9 +1169,6 @@
     <t>TC_DBS_02, TC_DBS_03</t>
   </si>
   <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>Failed</t>
   </si>
   <si>
@@ -1132,12 +1176,6 @@
   </si>
   <si>
     <t>Not Executed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	As expected.</t>
-  </si>
-  <si>
-    <t>The reactions column returns the count increased by one, matching the number shown in the UI.</t>
   </si>
 </sst>
 </file>
@@ -1547,19 +1585,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -1567,15 +1605,15 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="B2" s="2">
         <f>COUNTA('DB Posts'!A2:A100)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2">
         <f>COUNTIF('DB Posts'!H2:H100,"Passed")</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2">
         <f>COUNTIF('DB Posts'!H2:H100,"Failed")</f>
@@ -1583,7 +1621,7 @@
       </c>
       <c r="E2" s="2" t="str">
         <f t="shared" ref="E2:E9" si="0">IF(B2=0,"0%",TEXT((C2+D2)/B2,"0%"))</f>
-        <v>0%</v>
+        <v>70%</v>
       </c>
       <c r="F2" s="2" t="str">
         <f t="shared" ref="F2:F10" si="1">IF(D2&gt;0,"Blocked",IF(C2&gt;=B2,"Complete","In Progress"))</f>
@@ -1592,7 +1630,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <f>COUNTA('DB Comments'!A2:A100)</f>
@@ -1617,7 +1655,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTA('DB Reported Posts'!A2:A100)</f>
@@ -1642,7 +1680,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTA('DB Map Notes'!A2:A100)</f>
@@ -1667,7 +1705,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTA('DB Postcards'!A2:A100)</f>
@@ -1692,7 +1730,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTA('DB Bug Reports'!A2:A100)</f>
@@ -1717,7 +1755,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="B8" s="2">
         <f>COUNTA('DB Device Identities'!A2:A100)</f>
@@ -1742,7 +1780,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="B9" s="2">
         <f>COUNTA('DB Settings'!A2:A100)</f>
@@ -1767,15 +1805,15 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3">
         <f>SUM(B2:B9)</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" s="3">
         <f>SUM(C2:C9)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3">
         <f>SUM(D2:D9)</f>
@@ -1783,7 +1821,7 @@
       </c>
       <c r="E10" s="3" t="str">
         <f>TEXT((C10+D10)/B10,"0%")</f>
-        <v>0%</v>
+        <v>18%</v>
       </c>
       <c r="F10" s="3" t="str">
         <f t="shared" si="1"/>
@@ -1809,444 +1847,444 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>15</v>
+        <v>232</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -2270,22 +2308,22 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>331</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -2295,7 +2333,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -2340,217 +2378,289 @@
     </row>
     <row r="2" spans="1:9" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="H2" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I2" s="7" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="H3" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I3" s="7" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>336</v>
+        <v>29</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="H4" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I4" s="7" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+        <v>34</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I5" s="7" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+        <v>41</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I6" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I7" s="7" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I8" s="7" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="7" t="s">
-        <v>91</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="7" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I9" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:I11" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." promptTitle="Status" prompt="Choose from the list." xr:uid="{00000000-0002-0000-0100-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>Options!$A$2:$A$5</xm:f>
           </x14:formula1>
@@ -2609,127 +2719,127 @@
     </row>
     <row r="2" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>111</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>123</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2738,7 +2848,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." promptTitle="Status" prompt="Choose from the list." xr:uid="{00000000-0002-0000-0200-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." xr:uid="{00000000-0002-0000-0200-000000000000}">
           <x14:formula1>
             <xm:f>Options!$A$2:$A$5</xm:f>
           </x14:formula1>
@@ -2797,102 +2907,102 @@
     </row>
     <row r="2" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="7" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="7" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="7" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="7" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2901,7 +3011,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." promptTitle="Status" prompt="Choose from the list." xr:uid="{00000000-0002-0000-0300-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." xr:uid="{00000000-0002-0000-0300-000000000000}">
           <x14:formula1>
             <xm:f>Options!$A$2:$A$5</xm:f>
           </x14:formula1>
@@ -2960,127 +3070,127 @@
     </row>
     <row r="2" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="7" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="7" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -3089,7 +3199,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." promptTitle="Status" prompt="Choose from the list." xr:uid="{00000000-0002-0000-0400-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." xr:uid="{00000000-0002-0000-0400-000000000000}">
           <x14:formula1>
             <xm:f>Options!$A$2:$A$5</xm:f>
           </x14:formula1>
@@ -3148,102 +3258,102 @@
     </row>
     <row r="2" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="7" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="7" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="7" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="7" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -3252,7 +3362,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." promptTitle="Status" prompt="Choose from the list." xr:uid="{00000000-0002-0000-0500-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." xr:uid="{00000000-0002-0000-0500-000000000000}">
           <x14:formula1>
             <xm:f>Options!$A$2:$A$5</xm:f>
           </x14:formula1>
@@ -3311,102 +3421,102 @@
     </row>
     <row r="2" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="7" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="7" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="7" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="7" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3415,7 +3525,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." promptTitle="Status" prompt="Choose from the list." xr:uid="{00000000-0002-0000-0600-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." xr:uid="{00000000-0002-0000-0600-000000000000}">
           <x14:formula1>
             <xm:f>Options!$A$2:$A$5</xm:f>
           </x14:formula1>
@@ -3474,77 +3584,77 @@
     </row>
     <row r="2" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>226</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
+        <v>227</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>11</v>
+        <v>228</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>12</v>
+        <v>229</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>14</v>
+        <v>231</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="7" t="s">
-        <v>15</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>16</v>
+        <v>233</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>17</v>
+        <v>234</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>18</v>
+        <v>235</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>19</v>
+        <v>236</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="7" t="s">
-        <v>15</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>22</v>
+        <v>239</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>23</v>
+        <v>240</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>24</v>
+        <v>241</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>242</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>26</v>
+        <v>243</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>27</v>
+        <v>244</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="7" t="s">
-        <v>15</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -3553,7 +3663,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." promptTitle="Status" prompt="Choose from the list." xr:uid="{00000000-0002-0000-0700-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." xr:uid="{00000000-0002-0000-0700-000000000000}">
           <x14:formula1>
             <xm:f>Options!$A$2:$A$5</xm:f>
           </x14:formula1>
@@ -3612,102 +3722,102 @@
     </row>
     <row r="2" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="7" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="7" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="7" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="7" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -3716,7 +3826,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." promptTitle="Status" prompt="Choose from the list." xr:uid="{00000000-0002-0000-0800-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Please pick Passed, Failed, Blocked or Not Executed." xr:uid="{00000000-0002-0000-0800-000000000000}">
           <x14:formula1>
             <xm:f>Options!$A$2:$A$5</xm:f>
           </x14:formula1>

--- a/qa/manual/test-cases/Database/Database_testCase.xlsx
+++ b/qa/manual/test-cases/Database/Database_testCase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\freeSpace-main\qa\manual\test-cases\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8316D57D-0740-4956-BD50-EC63B0FCACD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A227BA9-3F94-47EC-9346-663C6EF4CB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="347">
   <si>
     <t>TC ID</t>
   </si>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="C2" s="2">
         <f>COUNTIF('DB Posts'!H2:H100,"Passed")</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2">
         <f>COUNTIF('DB Posts'!H2:H100,"Failed")</f>
@@ -1621,11 +1621,11 @@
       </c>
       <c r="E2" s="2" t="str">
         <f t="shared" ref="E2:E9" si="0">IF(B2=0,"0%",TEXT((C2+D2)/B2,"0%"))</f>
-        <v>70%</v>
+        <v>100%</v>
       </c>
       <c r="F2" s="2" t="str">
         <f t="shared" ref="F2:F10" si="1">IF(D2&gt;0,"Blocked",IF(C2&gt;=B2,"Complete","In Progress"))</f>
-        <v>In Progress</v>
+        <v>Complete</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C3" s="2">
         <f>COUNTIF('DB Comments'!H2:H100,"Passed")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2">
         <f>COUNTIF('DB Comments'!H2:H100,"Failed")</f>
@@ -1646,11 +1646,11 @@
       </c>
       <c r="E3" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>0%</v>
+        <v>100%</v>
       </c>
       <c r="F3" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>In Progress</v>
+        <v>Complete</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C10" s="3">
         <f>SUM(C2:C9)</f>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3">
         <f>SUM(D2:D9)</f>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="E10" s="3" t="str">
         <f>TEXT((C10+D10)/B10,"0%")</f>
-        <v>18%</v>
+        <v>38%</v>
       </c>
       <c r="F10" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2598,8 +2598,12 @@
       <c r="F9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I9" s="7" t="s">
         <v>59</v>
       </c>
@@ -2623,8 +2627,12 @@
       <c r="F10" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="G10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I10" s="7" t="s">
         <v>66</v>
       </c>
@@ -2648,8 +2656,12 @@
       <c r="F11" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="G11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I11" s="7" t="s">
         <v>73</v>
       </c>
@@ -2736,8 +2748,12 @@
       <c r="F2" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="G2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I2" s="7" t="s">
         <v>94</v>
       </c>
@@ -2761,8 +2777,12 @@
       <c r="F3" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="G3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I3" s="7" t="s">
         <v>101</v>
       </c>
@@ -2786,8 +2806,12 @@
       <c r="F4" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="G4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I4" s="7" t="s">
         <v>94</v>
       </c>
@@ -2811,8 +2835,12 @@
       <c r="F5" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="G5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I5" s="7" t="s">
         <v>94</v>
       </c>
@@ -2836,8 +2864,12 @@
       <c r="F6" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+      <c r="G6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="I6" s="7" t="s">
         <v>120</v>
       </c>
